--- a/Methyl/Panel 450 region_TMD.xlsx
+++ b/Methyl/Panel 450 region_TMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://genesolutionsvietnam-my.sharepoint.com/personal/vivan_genesolutions_vn/Documents/Reduce methylation panel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XN\du-an-dung-chung\Methyl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42A1D78B-E9F7-4B74-BC7E-625087F03202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C48F27-184C-4AAE-AB03-98D0388E76A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{5A1DF7B9-B783-4D0C-AD68-DCFE6D7B4350}"/>
+    <workbookView minimized="1" xWindow="2850" yWindow="2850" windowWidth="15375" windowHeight="7785" xr2:uid="{5A1DF7B9-B783-4D0C-AD68-DCFE6D7B4350}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -3960,7 +3958,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3994,7 +3992,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4327,7 +4325,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63ED2DC4-22B7-4A57-A7CE-88FE11542035}">
   <dimension ref="A1:F451"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
@@ -4336,7 +4334,7 @@
     <col min="6" max="6" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4356,7 +4354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -4376,7 +4374,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4396,7 +4394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -4416,7 +4414,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -4436,7 +4434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -4456,7 +4454,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4476,7 +4474,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -4496,7 +4494,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -4516,7 +4514,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -4536,7 +4534,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -4556,7 +4554,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -4576,7 +4574,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -4596,7 +4594,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -4616,7 +4614,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -4636,7 +4634,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -4656,7 +4654,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -4676,7 +4674,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -4696,7 +4694,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -4716,7 +4714,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -4736,7 +4734,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -4756,7 +4754,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -4776,7 +4774,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -4796,7 +4794,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -4816,7 +4814,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -4836,7 +4834,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -4856,7 +4854,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -4876,7 +4874,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -4896,7 +4894,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -4916,7 +4914,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -4936,7 +4934,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -4956,7 +4954,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -4976,7 +4974,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -4996,7 +4994,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -5016,7 +5014,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -5036,7 +5034,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -5056,7 +5054,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -5076,7 +5074,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -5096,7 +5094,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -5116,7 +5114,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -5136,7 +5134,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -5156,7 +5154,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -5176,7 +5174,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -5196,7 +5194,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -5216,7 +5214,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -5236,7 +5234,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>128</v>
       </c>
@@ -5256,7 +5254,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>128</v>
       </c>
@@ -5276,7 +5274,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>128</v>
       </c>
@@ -5296,7 +5294,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>128</v>
       </c>
@@ -5316,7 +5314,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>128</v>
       </c>
@@ -5336,7 +5334,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>128</v>
       </c>
@@ -5356,7 +5354,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>128</v>
       </c>
@@ -5376,7 +5374,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>128</v>
       </c>
@@ -5396,7 +5394,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>128</v>
       </c>
@@ -5416,7 +5414,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>128</v>
       </c>
@@ -5436,7 +5434,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>128</v>
       </c>
@@ -5456,7 +5454,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>128</v>
       </c>
@@ -5476,7 +5474,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>128</v>
       </c>
@@ -5496,7 +5494,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>128</v>
       </c>
@@ -5516,7 +5514,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>128</v>
       </c>
@@ -5536,7 +5534,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>128</v>
       </c>
@@ -5556,7 +5554,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -5576,7 +5574,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>128</v>
       </c>
@@ -5596,7 +5594,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>128</v>
       </c>
@@ -5616,7 +5614,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>128</v>
       </c>
@@ -5636,7 +5634,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>128</v>
       </c>
@@ -5656,7 +5654,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>128</v>
       </c>
@@ -5676,7 +5674,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>128</v>
       </c>
@@ -5696,7 +5694,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>128</v>
       </c>
@@ -5716,7 +5714,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>128</v>
       </c>
@@ -5736,7 +5734,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>128</v>
       </c>
@@ -5756,7 +5754,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>128</v>
       </c>
@@ -5776,7 +5774,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>128</v>
       </c>
@@ -5796,7 +5794,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>128</v>
       </c>
@@ -5816,7 +5814,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>128</v>
       </c>
@@ -5836,7 +5834,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>128</v>
       </c>
@@ -5856,7 +5854,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>128</v>
       </c>
@@ -5876,7 +5874,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>128</v>
       </c>
@@ -5896,7 +5894,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>128</v>
       </c>
@@ -5916,7 +5914,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>128</v>
       </c>
@@ -5936,7 +5934,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>128</v>
       </c>
@@ -5956,7 +5954,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>128</v>
       </c>
@@ -5976,7 +5974,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>128</v>
       </c>
@@ -5996,7 +5994,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>128</v>
       </c>
@@ -6016,7 +6014,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>128</v>
       </c>
@@ -6036,7 +6034,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>128</v>
       </c>
@@ -6056,7 +6054,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>128</v>
       </c>
@@ -6076,7 +6074,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>128</v>
       </c>
@@ -6096,7 +6094,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>128</v>
       </c>
@@ -6116,7 +6114,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>128</v>
       </c>
@@ -6136,7 +6134,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>128</v>
       </c>
@@ -6156,7 +6154,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>128</v>
       </c>
@@ -6176,7 +6174,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>128</v>
       </c>
@@ -6196,7 +6194,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>128</v>
       </c>
@@ -6216,7 +6214,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>128</v>
       </c>
@@ -6236,7 +6234,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>128</v>
       </c>
@@ -6256,7 +6254,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>128</v>
       </c>
@@ -6276,7 +6274,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>277</v>
       </c>
@@ -6296,7 +6294,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>277</v>
       </c>
@@ -6316,7 +6314,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>277</v>
       </c>
@@ -6336,7 +6334,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>277</v>
       </c>
@@ -6356,7 +6354,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>277</v>
       </c>
@@ -6376,7 +6374,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>277</v>
       </c>
@@ -6396,7 +6394,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>277</v>
       </c>
@@ -6416,7 +6414,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>277</v>
       </c>
@@ -6436,7 +6434,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>277</v>
       </c>
@@ -6456,7 +6454,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>277</v>
       </c>
@@ -6476,7 +6474,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>277</v>
       </c>
@@ -6496,7 +6494,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>277</v>
       </c>
@@ -6516,7 +6514,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>277</v>
       </c>
@@ -6536,7 +6534,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>277</v>
       </c>
@@ -6556,7 +6554,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>277</v>
       </c>
@@ -6576,7 +6574,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>277</v>
       </c>
@@ -6596,7 +6594,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>277</v>
       </c>
@@ -6616,7 +6614,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>326</v>
       </c>
@@ -6636,7 +6634,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>326</v>
       </c>
@@ -6656,7 +6654,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>326</v>
       </c>
@@ -6676,7 +6674,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>326</v>
       </c>
@@ -6696,7 +6694,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>326</v>
       </c>
@@ -6716,7 +6714,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>326</v>
       </c>
@@ -6736,7 +6734,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>326</v>
       </c>
@@ -6756,7 +6754,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>326</v>
       </c>
@@ -6776,7 +6774,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>326</v>
       </c>
@@ -6796,7 +6794,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>326</v>
       </c>
@@ -6816,7 +6814,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>326</v>
       </c>
@@ -6836,7 +6834,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>326</v>
       </c>
@@ -6856,7 +6854,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>326</v>
       </c>
@@ -6876,7 +6874,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>326</v>
       </c>
@@ -6896,7 +6894,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>326</v>
       </c>
@@ -6916,7 +6914,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>326</v>
       </c>
@@ -6936,7 +6934,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>326</v>
       </c>
@@ -6956,7 +6954,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>326</v>
       </c>
@@ -6976,7 +6974,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>326</v>
       </c>
@@ -6996,7 +6994,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>326</v>
       </c>
@@ -7016,7 +7014,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>326</v>
       </c>
@@ -7036,7 +7034,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>326</v>
       </c>
@@ -7056,7 +7054,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>326</v>
       </c>
@@ -7076,7 +7074,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>393</v>
       </c>
@@ -7096,7 +7094,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>393</v>
       </c>
@@ -7116,7 +7114,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>393</v>
       </c>
@@ -7136,7 +7134,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>393</v>
       </c>
@@ -7156,7 +7154,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>393</v>
       </c>
@@ -7176,7 +7174,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>393</v>
       </c>
@@ -7196,7 +7194,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>393</v>
       </c>
@@ -7216,7 +7214,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>393</v>
       </c>
@@ -7236,7 +7234,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>393</v>
       </c>
@@ -7256,7 +7254,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>393</v>
       </c>
@@ -7276,7 +7274,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>393</v>
       </c>
@@ -7296,7 +7294,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>393</v>
       </c>
@@ -7316,7 +7314,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>393</v>
       </c>
@@ -7336,7 +7334,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>393</v>
       </c>
@@ -7356,7 +7354,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>393</v>
       </c>
@@ -7376,7 +7374,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>393</v>
       </c>
@@ -7396,7 +7394,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>393</v>
       </c>
@@ -7416,7 +7414,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>393</v>
       </c>
@@ -7436,7 +7434,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>393</v>
       </c>
@@ -7456,7 +7454,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>393</v>
       </c>
@@ -7476,7 +7474,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>393</v>
       </c>
@@ -7496,7 +7494,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>455</v>
       </c>
@@ -7516,7 +7514,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>455</v>
       </c>
@@ -7536,7 +7534,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>455</v>
       </c>
@@ -7556,7 +7554,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>455</v>
       </c>
@@ -7576,7 +7574,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>455</v>
       </c>
@@ -7596,7 +7594,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>455</v>
       </c>
@@ -7616,7 +7614,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>455</v>
       </c>
@@ -7636,7 +7634,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>455</v>
       </c>
@@ -7656,7 +7654,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>455</v>
       </c>
@@ -7676,7 +7674,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>455</v>
       </c>
@@ -7696,7 +7694,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>455</v>
       </c>
@@ -7716,7 +7714,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>455</v>
       </c>
@@ -7736,7 +7734,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>455</v>
       </c>
@@ -7756,7 +7754,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>455</v>
       </c>
@@ -7776,7 +7774,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>455</v>
       </c>
@@ -7796,7 +7794,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>455</v>
       </c>
@@ -7816,7 +7814,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>455</v>
       </c>
@@ -7836,7 +7834,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>455</v>
       </c>
@@ -7856,7 +7854,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>455</v>
       </c>
@@ -7876,7 +7874,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>455</v>
       </c>
@@ -7896,7 +7894,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>455</v>
       </c>
@@ -7916,7 +7914,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>455</v>
       </c>
@@ -7936,7 +7934,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>455</v>
       </c>
@@ -7956,7 +7954,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>455</v>
       </c>
@@ -7976,7 +7974,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>526</v>
       </c>
@@ -7996,7 +7994,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>526</v>
       </c>
@@ -8016,7 +8014,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>526</v>
       </c>
@@ -8036,7 +8034,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>526</v>
       </c>
@@ -8056,7 +8054,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>526</v>
       </c>
@@ -8076,7 +8074,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>526</v>
       </c>
@@ -8096,7 +8094,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>526</v>
       </c>
@@ -8116,7 +8114,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>526</v>
       </c>
@@ -8136,7 +8134,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>526</v>
       </c>
@@ -8156,7 +8154,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>526</v>
       </c>
@@ -8176,7 +8174,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>526</v>
       </c>
@@ -8196,7 +8194,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>526</v>
       </c>
@@ -8216,7 +8214,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>526</v>
       </c>
@@ -8236,7 +8234,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>526</v>
       </c>
@@ -8256,7 +8254,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>526</v>
       </c>
@@ -8276,7 +8274,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>526</v>
       </c>
@@ -8296,7 +8294,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>526</v>
       </c>
@@ -8316,7 +8314,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>526</v>
       </c>
@@ -8336,7 +8334,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>526</v>
       </c>
@@ -8356,7 +8354,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>526</v>
       </c>
@@ -8376,7 +8374,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>526</v>
       </c>
@@ -8396,7 +8394,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>526</v>
       </c>
@@ -8416,7 +8414,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>526</v>
       </c>
@@ -8436,7 +8434,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>526</v>
       </c>
@@ -8456,7 +8454,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>526</v>
       </c>
@@ -8476,7 +8474,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>526</v>
       </c>
@@ -8496,7 +8494,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>526</v>
       </c>
@@ -8516,7 +8514,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>526</v>
       </c>
@@ -8536,7 +8534,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>526</v>
       </c>
@@ -8556,7 +8554,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>526</v>
       </c>
@@ -8576,7 +8574,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>526</v>
       </c>
@@ -8596,7 +8594,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="214" spans="1:6">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>526</v>
       </c>
@@ -8616,7 +8614,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>617</v>
       </c>
@@ -8636,7 +8634,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>617</v>
       </c>
@@ -8656,7 +8654,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>617</v>
       </c>
@@ -8676,7 +8674,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>617</v>
       </c>
@@ -8696,7 +8694,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>617</v>
       </c>
@@ -8716,7 +8714,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>617</v>
       </c>
@@ -8736,7 +8734,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>617</v>
       </c>
@@ -8756,7 +8754,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>617</v>
       </c>
@@ -8776,7 +8774,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>617</v>
       </c>
@@ -8796,7 +8794,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>617</v>
       </c>
@@ -8816,7 +8814,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>617</v>
       </c>
@@ -8836,7 +8834,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>617</v>
       </c>
@@ -8856,7 +8854,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>617</v>
       </c>
@@ -8876,7 +8874,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>617</v>
       </c>
@@ -8896,7 +8894,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>617</v>
       </c>
@@ -8916,7 +8914,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>617</v>
       </c>
@@ -8936,7 +8934,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>617</v>
       </c>
@@ -8956,7 +8954,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>617</v>
       </c>
@@ -8976,7 +8974,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>617</v>
       </c>
@@ -8996,7 +8994,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>617</v>
       </c>
@@ -9016,7 +9014,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="235" spans="1:6">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>617</v>
       </c>
@@ -9036,7 +9034,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="236" spans="1:6">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>617</v>
       </c>
@@ -9056,7 +9054,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>617</v>
       </c>
@@ -9076,7 +9074,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>617</v>
       </c>
@@ -9096,7 +9094,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="239" spans="1:6">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>617</v>
       </c>
@@ -9116,7 +9114,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>690</v>
       </c>
@@ -9136,7 +9134,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="241" spans="1:6">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>690</v>
       </c>
@@ -9156,7 +9154,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="242" spans="1:6">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>690</v>
       </c>
@@ -9176,7 +9174,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="243" spans="1:6">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>690</v>
       </c>
@@ -9196,7 +9194,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>690</v>
       </c>
@@ -9216,7 +9214,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="245" spans="1:6">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>690</v>
       </c>
@@ -9236,7 +9234,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="246" spans="1:6">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>690</v>
       </c>
@@ -9256,7 +9254,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>690</v>
       </c>
@@ -9276,7 +9274,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>690</v>
       </c>
@@ -9296,7 +9294,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>690</v>
       </c>
@@ -9316,7 +9314,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="250" spans="1:6">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>690</v>
       </c>
@@ -9336,7 +9334,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>690</v>
       </c>
@@ -9356,7 +9354,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="252" spans="1:6">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>690</v>
       </c>
@@ -9376,7 +9374,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="253" spans="1:6">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>690</v>
       </c>
@@ -9396,7 +9394,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>690</v>
       </c>
@@ -9416,7 +9414,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>690</v>
       </c>
@@ -9436,7 +9434,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="256" spans="1:6">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>690</v>
       </c>
@@ -9456,7 +9454,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>690</v>
       </c>
@@ -9476,7 +9474,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="258" spans="1:6">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>742</v>
       </c>
@@ -9496,7 +9494,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>742</v>
       </c>
@@ -9516,7 +9514,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>742</v>
       </c>
@@ -9536,7 +9534,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>742</v>
       </c>
@@ -9556,7 +9554,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>742</v>
       </c>
@@ -9576,7 +9574,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>742</v>
       </c>
@@ -9596,7 +9594,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="264" spans="1:6">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>742</v>
       </c>
@@ -9616,7 +9614,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>742</v>
       </c>
@@ -9636,7 +9634,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="266" spans="1:6">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>742</v>
       </c>
@@ -9656,7 +9654,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="267" spans="1:6">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>742</v>
       </c>
@@ -9676,7 +9674,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>742</v>
       </c>
@@ -9696,7 +9694,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="269" spans="1:6">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>742</v>
       </c>
@@ -9716,7 +9714,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="270" spans="1:6">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>742</v>
       </c>
@@ -9736,7 +9734,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>742</v>
       </c>
@@ -9756,7 +9754,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="272" spans="1:6">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>742</v>
       </c>
@@ -9776,7 +9774,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="273" spans="1:6">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>742</v>
       </c>
@@ -9796,7 +9794,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>742</v>
       </c>
@@ -9816,7 +9814,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>742</v>
       </c>
@@ -9836,7 +9834,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>742</v>
       </c>
@@ -9856,7 +9854,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="277" spans="1:6">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>742</v>
       </c>
@@ -9876,7 +9874,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="278" spans="1:6">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>742</v>
       </c>
@@ -9896,7 +9894,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="279" spans="1:6">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>742</v>
       </c>
@@ -9916,7 +9914,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="280" spans="1:6">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>742</v>
       </c>
@@ -9936,7 +9934,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="281" spans="1:6">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>742</v>
       </c>
@@ -9956,7 +9954,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="282" spans="1:6">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>742</v>
       </c>
@@ -9976,7 +9974,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="283" spans="1:6">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>742</v>
       </c>
@@ -9996,7 +9994,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="284" spans="1:6">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>742</v>
       </c>
@@ -10016,7 +10014,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="285" spans="1:6">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>742</v>
       </c>
@@ -10036,7 +10034,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="286" spans="1:6">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>742</v>
       </c>
@@ -10056,7 +10054,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="287" spans="1:6">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>742</v>
       </c>
@@ -10076,7 +10074,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="288" spans="1:6">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>742</v>
       </c>
@@ -10096,7 +10094,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="289" spans="1:6">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>742</v>
       </c>
@@ -10116,7 +10114,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="290" spans="1:6">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>742</v>
       </c>
@@ -10136,7 +10134,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="291" spans="1:6">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>742</v>
       </c>
@@ -10156,7 +10154,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="292" spans="1:6">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>838</v>
       </c>
@@ -10176,7 +10174,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="293" spans="1:6">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>838</v>
       </c>
@@ -10196,7 +10194,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>838</v>
       </c>
@@ -10216,7 +10214,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="295" spans="1:6">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>838</v>
       </c>
@@ -10236,7 +10234,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="296" spans="1:6">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>838</v>
       </c>
@@ -10256,7 +10254,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="297" spans="1:6">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>838</v>
       </c>
@@ -10276,7 +10274,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="298" spans="1:6">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>838</v>
       </c>
@@ -10296,7 +10294,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="299" spans="1:6">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>838</v>
       </c>
@@ -10316,7 +10314,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="300" spans="1:6">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>838</v>
       </c>
@@ -10336,7 +10334,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="301" spans="1:6">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>838</v>
       </c>
@@ -10356,7 +10354,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="302" spans="1:6">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>838</v>
       </c>
@@ -10376,7 +10374,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="303" spans="1:6">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>838</v>
       </c>
@@ -10396,7 +10394,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="304" spans="1:6">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>838</v>
       </c>
@@ -10416,7 +10414,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="305" spans="1:6">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>838</v>
       </c>
@@ -10436,7 +10434,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="306" spans="1:6">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>838</v>
       </c>
@@ -10456,7 +10454,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="307" spans="1:6">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>838</v>
       </c>
@@ -10476,7 +10474,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="308" spans="1:6">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>838</v>
       </c>
@@ -10496,7 +10494,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="309" spans="1:6">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>888</v>
       </c>
@@ -10516,7 +10514,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="310" spans="1:6">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>888</v>
       </c>
@@ -10536,7 +10534,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="311" spans="1:6">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>888</v>
       </c>
@@ -10556,7 +10554,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="312" spans="1:6">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>888</v>
       </c>
@@ -10576,7 +10574,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="313" spans="1:6">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>888</v>
       </c>
@@ -10596,7 +10594,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="314" spans="1:6">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>888</v>
       </c>
@@ -10616,7 +10614,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="315" spans="1:6">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>888</v>
       </c>
@@ -10636,7 +10634,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="316" spans="1:6">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>888</v>
       </c>
@@ -10656,7 +10654,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="317" spans="1:6">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>888</v>
       </c>
@@ -10676,7 +10674,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="318" spans="1:6">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>888</v>
       </c>
@@ -10696,7 +10694,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="319" spans="1:6">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>888</v>
       </c>
@@ -10716,7 +10714,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="320" spans="1:6">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>888</v>
       </c>
@@ -10736,7 +10734,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="321" spans="1:6">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>888</v>
       </c>
@@ -10756,7 +10754,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="322" spans="1:6">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>888</v>
       </c>
@@ -10776,7 +10774,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="323" spans="1:6">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>888</v>
       </c>
@@ -10796,7 +10794,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="324" spans="1:6">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>888</v>
       </c>
@@ -10816,7 +10814,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="325" spans="1:6">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>888</v>
       </c>
@@ -10836,7 +10834,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="326" spans="1:6">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>888</v>
       </c>
@@ -10856,7 +10854,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="327" spans="1:6">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>888</v>
       </c>
@@ -10876,7 +10874,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="328" spans="1:6">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>888</v>
       </c>
@@ -10896,7 +10894,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="329" spans="1:6">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>888</v>
       </c>
@@ -10916,7 +10914,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="330" spans="1:6">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>888</v>
       </c>
@@ -10936,7 +10934,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="331" spans="1:6">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>888</v>
       </c>
@@ -10956,7 +10954,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="332" spans="1:6">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>888</v>
       </c>
@@ -10976,7 +10974,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="333" spans="1:6">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>888</v>
       </c>
@@ -10996,7 +10994,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="334" spans="1:6">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>888</v>
       </c>
@@ -11016,7 +11014,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="335" spans="1:6">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>888</v>
       </c>
@@ -11036,7 +11034,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="336" spans="1:6">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>888</v>
       </c>
@@ -11056,7 +11054,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="337" spans="1:6">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>966</v>
       </c>
@@ -11076,7 +11074,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="338" spans="1:6">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>966</v>
       </c>
@@ -11096,7 +11094,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="339" spans="1:6">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>966</v>
       </c>
@@ -11116,7 +11114,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="340" spans="1:6">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>966</v>
       </c>
@@ -11136,7 +11134,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="341" spans="1:6">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>966</v>
       </c>
@@ -11156,7 +11154,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="342" spans="1:6">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>966</v>
       </c>
@@ -11176,7 +11174,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="343" spans="1:6">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>966</v>
       </c>
@@ -11196,7 +11194,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="344" spans="1:6">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>966</v>
       </c>
@@ -11216,7 +11214,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="345" spans="1:6">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>966</v>
       </c>
@@ -11236,7 +11234,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="346" spans="1:6">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>966</v>
       </c>
@@ -11256,7 +11254,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="347" spans="1:6">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>966</v>
       </c>
@@ -11276,7 +11274,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="348" spans="1:6">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>966</v>
       </c>
@@ -11296,7 +11294,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="349" spans="1:6">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>966</v>
       </c>
@@ -11316,7 +11314,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="350" spans="1:6">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>966</v>
       </c>
@@ -11336,7 +11334,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="351" spans="1:6">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>966</v>
       </c>
@@ -11356,7 +11354,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="352" spans="1:6">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1010</v>
       </c>
@@ -11376,7 +11374,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="353" spans="1:6">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1010</v>
       </c>
@@ -11396,7 +11394,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="354" spans="1:6">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1010</v>
       </c>
@@ -11416,7 +11414,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="355" spans="1:6">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1010</v>
       </c>
@@ -11436,7 +11434,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="356" spans="1:6">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1010</v>
       </c>
@@ -11456,7 +11454,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="357" spans="1:6">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1010</v>
       </c>
@@ -11476,7 +11474,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="358" spans="1:6">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1010</v>
       </c>
@@ -11496,7 +11494,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="359" spans="1:6">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1010</v>
       </c>
@@ -11516,7 +11514,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="360" spans="1:6">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1010</v>
       </c>
@@ -11536,7 +11534,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="361" spans="1:6">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1010</v>
       </c>
@@ -11556,7 +11554,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="362" spans="1:6">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1010</v>
       </c>
@@ -11576,7 +11574,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="363" spans="1:6">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1010</v>
       </c>
@@ -11596,7 +11594,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="364" spans="1:6">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1010</v>
       </c>
@@ -11616,7 +11614,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="365" spans="1:6">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1010</v>
       </c>
@@ -11636,7 +11634,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="366" spans="1:6">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1010</v>
       </c>
@@ -11656,7 +11654,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="367" spans="1:6">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1054</v>
       </c>
@@ -11676,7 +11674,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="368" spans="1:6">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1054</v>
       </c>
@@ -11696,7 +11694,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="369" spans="1:6">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1054</v>
       </c>
@@ -11716,7 +11714,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="370" spans="1:6">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1054</v>
       </c>
@@ -11736,7 +11734,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="371" spans="1:6">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1054</v>
       </c>
@@ -11756,7 +11754,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="372" spans="1:6">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1054</v>
       </c>
@@ -11776,7 +11774,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="373" spans="1:6">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1054</v>
       </c>
@@ -11796,7 +11794,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="374" spans="1:6">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1054</v>
       </c>
@@ -11816,7 +11814,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="375" spans="1:6">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1054</v>
       </c>
@@ -11836,7 +11834,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="376" spans="1:6">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1080</v>
       </c>
@@ -11856,7 +11854,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="377" spans="1:6">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1080</v>
       </c>
@@ -11876,7 +11874,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="378" spans="1:6">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1080</v>
       </c>
@@ -11896,7 +11894,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="379" spans="1:6">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1080</v>
       </c>
@@ -11916,7 +11914,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="380" spans="1:6">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1080</v>
       </c>
@@ -11936,7 +11934,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="381" spans="1:6">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1080</v>
       </c>
@@ -11956,7 +11954,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="382" spans="1:6">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1080</v>
       </c>
@@ -11976,7 +11974,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="383" spans="1:6">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1080</v>
       </c>
@@ -11996,7 +11994,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="384" spans="1:6">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1080</v>
       </c>
@@ -12016,7 +12014,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="385" spans="1:6">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1080</v>
       </c>
@@ -12036,7 +12034,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="386" spans="1:6">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1080</v>
       </c>
@@ -12056,7 +12054,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="387" spans="1:6">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1080</v>
       </c>
@@ -12076,7 +12074,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="388" spans="1:6">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1080</v>
       </c>
@@ -12096,7 +12094,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="389" spans="1:6">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1118</v>
       </c>
@@ -12116,7 +12114,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="390" spans="1:6">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1118</v>
       </c>
@@ -12136,7 +12134,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="391" spans="1:6">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1118</v>
       </c>
@@ -12156,7 +12154,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="392" spans="1:6">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1118</v>
       </c>
@@ -12176,7 +12174,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="393" spans="1:6">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1118</v>
       </c>
@@ -12196,7 +12194,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="394" spans="1:6">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1118</v>
       </c>
@@ -12216,7 +12214,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="395" spans="1:6">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1118</v>
       </c>
@@ -12236,7 +12234,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="396" spans="1:6">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1118</v>
       </c>
@@ -12256,7 +12254,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="397" spans="1:6">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1118</v>
       </c>
@@ -12276,7 +12274,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="398" spans="1:6">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1118</v>
       </c>
@@ -12296,7 +12294,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="399" spans="1:6">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1118</v>
       </c>
@@ -12316,7 +12314,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="400" spans="1:6">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1118</v>
       </c>
@@ -12336,7 +12334,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="401" spans="1:6">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1118</v>
       </c>
@@ -12356,7 +12354,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="402" spans="1:6">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1118</v>
       </c>
@@ -12376,7 +12374,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="403" spans="1:6">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1118</v>
       </c>
@@ -12396,7 +12394,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="404" spans="1:6">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1118</v>
       </c>
@@ -12416,7 +12414,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="405" spans="1:6">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1118</v>
       </c>
@@ -12436,7 +12434,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="406" spans="1:6">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1118</v>
       </c>
@@ -12456,7 +12454,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="407" spans="1:6">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1118</v>
       </c>
@@ -12476,7 +12474,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="408" spans="1:6">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1118</v>
       </c>
@@ -12496,7 +12494,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="409" spans="1:6">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1118</v>
       </c>
@@ -12516,7 +12514,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="410" spans="1:6">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1118</v>
       </c>
@@ -12536,7 +12534,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="411" spans="1:6">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1118</v>
       </c>
@@ -12556,7 +12554,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="412" spans="1:6">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1118</v>
       </c>
@@ -12576,7 +12574,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="413" spans="1:6">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1118</v>
       </c>
@@ -12596,7 +12594,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="414" spans="1:6">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1189</v>
       </c>
@@ -12616,7 +12614,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="415" spans="1:6">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1189</v>
       </c>
@@ -12636,7 +12634,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="416" spans="1:6">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1189</v>
       </c>
@@ -12656,7 +12654,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="417" spans="1:6">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1199</v>
       </c>
@@ -12676,7 +12674,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="418" spans="1:6">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1199</v>
       </c>
@@ -12696,7 +12694,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="419" spans="1:6">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1199</v>
       </c>
@@ -12716,7 +12714,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="420" spans="1:6">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1199</v>
       </c>
@@ -12736,7 +12734,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="421" spans="1:6">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1199</v>
       </c>
@@ -12756,7 +12754,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="422" spans="1:6">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1199</v>
       </c>
@@ -12776,7 +12774,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="423" spans="1:6">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1199</v>
       </c>
@@ -12796,7 +12794,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="424" spans="1:6">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1199</v>
       </c>
@@ -12816,7 +12814,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="425" spans="1:6">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1199</v>
       </c>
@@ -12836,7 +12834,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="426" spans="1:6">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1199</v>
       </c>
@@ -12856,7 +12854,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="427" spans="1:6">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1199</v>
       </c>
@@ -12876,7 +12874,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="428" spans="1:6">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1199</v>
       </c>
@@ -12896,7 +12894,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="429" spans="1:6">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1199</v>
       </c>
@@ -12916,7 +12914,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="430" spans="1:6">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1238</v>
       </c>
@@ -12936,7 +12934,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="431" spans="1:6">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1238</v>
       </c>
@@ -12956,7 +12954,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="432" spans="1:6">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1238</v>
       </c>
@@ -12976,7 +12974,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="433" spans="1:6">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1238</v>
       </c>
@@ -12996,7 +12994,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="434" spans="1:6">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1238</v>
       </c>
@@ -13016,7 +13014,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="435" spans="1:6">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1238</v>
       </c>
@@ -13036,7 +13034,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="436" spans="1:6">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1238</v>
       </c>
@@ -13056,7 +13054,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="437" spans="1:6">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1260</v>
       </c>
@@ -13076,7 +13074,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="438" spans="1:6">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1260</v>
       </c>
@@ -13096,7 +13094,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="439" spans="1:6">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1260</v>
       </c>
@@ -13116,7 +13114,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="440" spans="1:6">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1260</v>
       </c>
@@ -13136,7 +13134,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="441" spans="1:6">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1272</v>
       </c>
@@ -13156,7 +13154,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="442" spans="1:6">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1272</v>
       </c>
@@ -13176,7 +13174,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="443" spans="1:6">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1272</v>
       </c>
@@ -13196,7 +13194,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="444" spans="1:6">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1272</v>
       </c>
@@ -13216,7 +13214,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="445" spans="1:6">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1272</v>
       </c>
@@ -13236,7 +13234,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="446" spans="1:6">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1272</v>
       </c>
@@ -13256,7 +13254,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="447" spans="1:6">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1272</v>
       </c>
@@ -13276,7 +13274,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="448" spans="1:6">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1272</v>
       </c>
@@ -13296,7 +13294,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="449" spans="1:6">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1272</v>
       </c>
@@ -13316,7 +13314,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="450" spans="1:6">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1272</v>
       </c>
@@ -13336,7 +13334,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="451" spans="1:6">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1272</v>
       </c>
